--- a/data/trans_orig/IP2903-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2903-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28009</t>
+          <t>28516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43141</t>
+          <t>43677</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27412</t>
+          <t>27215</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41211</t>
+          <t>41313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58826</t>
+          <t>59916</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79020</t>
+          <t>79815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10821</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22530</t>
+          <t>22653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10498</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>21750</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24179</t>
+          <t>24018</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>40433</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29726</t>
+          <t>29632</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>44648</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27492</t>
+          <t>27352</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42278</t>
+          <t>41692</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61441</t>
+          <t>61442</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81964</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>46,85%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112044</t>
+          <t>111851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>141375</t>
+          <t>142668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135078</t>
+          <t>136574</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>167800</t>
+          <t>167728</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>256042</t>
+          <t>257440</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>300801</t>
+          <t>299947</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68185</t>
+          <t>68639</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93233</t>
+          <t>91751</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94861</t>
+          <t>94909</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>124396</t>
+          <t>123162</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>170396</t>
+          <t>171416</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>209170</t>
+          <t>209296</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>178250</t>
+          <t>177658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>209746</t>
+          <t>210060</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>181508</t>
+          <t>181783</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>215509</t>
+          <t>215925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>369192</t>
+          <t>367500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>415239</t>
+          <t>415245</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40647</t>
+          <t>42825</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61433</t>
+          <t>61611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>31132</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48899</t>
+          <t>48082</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>79192</t>
+          <t>78235</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>104382</t>
+          <t>104112</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28625</t>
+          <t>28830</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45841</t>
+          <t>46231</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31830</t>
+          <t>32965</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50269</t>
+          <t>50596</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66413</t>
+          <t>65445</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91306</t>
+          <t>90973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67721</t>
+          <t>68525</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89132</t>
+          <t>88653</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62818</t>
+          <t>62489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82259</t>
+          <t>81414</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137248</t>
+          <t>135976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>164453</t>
+          <t>165675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>194118</t>
+          <t>192578</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>232729</t>
+          <t>231965</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>205214</t>
+          <t>206357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>245134</t>
+          <t>245801</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>410685</t>
+          <t>412306</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>465303</t>
+          <t>466016</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118186</t>
+          <t>118225</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151356</t>
+          <t>150886</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>146300</t>
+          <t>145975</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>182591</t>
+          <t>183928</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274202</t>
+          <t>274336</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>325819</t>
+          <t>323500</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>289042</t>
+          <t>288312</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>330723</t>
+          <t>328554</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>284118</t>
+          <t>283820</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>325097</t>
+          <t>326446</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>586436</t>
+          <t>585764</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>643618</t>
+          <t>642820</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,57%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29052</t>
+          <t>29175</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44337</t>
+          <t>45190</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22107</t>
+          <t>22847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36704</t>
+          <t>38218</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55698</t>
+          <t>55876</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77887</t>
+          <t>76576</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,02%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23406</t>
+          <t>24527</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20217</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23449</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40219</t>
+          <t>39719</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30128</t>
+          <t>30332</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45934</t>
+          <t>45293</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32647</t>
+          <t>30603</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47248</t>
+          <t>46849</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66205</t>
+          <t>66707</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88795</t>
+          <t>88454</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,84%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>158007</t>
+          <t>155106</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>189146</t>
+          <t>189745</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>169877</t>
+          <t>171165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>208401</t>
+          <t>205715</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>335585</t>
+          <t>334576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>384883</t>
+          <t>384982</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,49%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62213</t>
+          <t>62823</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86749</t>
+          <t>87931</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82944</t>
+          <t>84568</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>113050</t>
+          <t>112148</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>152811</t>
+          <t>153211</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>192500</t>
+          <t>193325</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>180045</t>
+          <t>180301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>213751</t>
+          <t>215195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>177627</t>
+          <t>180112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>217373</t>
+          <t>217125</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>371822</t>
+          <t>371223</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>421055</t>
+          <t>419403</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39948</t>
+          <t>41093</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59291</t>
+          <t>60745</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51360</t>
+          <t>50131</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72381</t>
+          <t>71382</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>97335</t>
+          <t>96666</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>127369</t>
+          <t>124812</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>37,84%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23550</t>
+          <t>22846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39544</t>
+          <t>39242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35425</t>
+          <t>34802</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52775</t>
+          <t>54214</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62446</t>
+          <t>61408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88755</t>
+          <t>86836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70703</t>
+          <t>70514</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91588</t>
+          <t>92141</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51528</t>
+          <t>52917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72694</t>
+          <t>73960</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128286</t>
+          <t>128959</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>158799</t>
+          <t>158939</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,19%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>240259</t>
+          <t>239779</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>281544</t>
+          <t>280987</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>257407</t>
+          <t>256753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>300108</t>
+          <t>300163</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>505689</t>
+          <t>509591</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>565297</t>
+          <t>570095</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104329</t>
+          <t>105783</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137504</t>
+          <t>138761</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136993</t>
+          <t>137588</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>173035</t>
+          <t>175244</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>253113</t>
+          <t>252263</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>301556</t>
+          <t>302481</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>297192</t>
+          <t>294882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>338627</t>
+          <t>338753</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>278065</t>
+          <t>278380</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>324254</t>
+          <t>322306</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>585328</t>
+          <t>584073</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>649813</t>
+          <t>650109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,41%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11858</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22768</t>
+          <t>23086</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>15151</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>27527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29460</t>
+          <t>28918</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46318</t>
+          <t>46610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12576</t>
+          <t>12788</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23491</t>
+          <t>23876</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>15638</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28348</t>
+          <t>28727</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31668</t>
+          <t>31390</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48234</t>
+          <t>48012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>17601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>29304</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>18328</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31362</t>
+          <t>31983</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39081</t>
+          <t>40038</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57348</t>
+          <t>58208</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>121005</t>
+          <t>122669</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154443</t>
+          <t>154811</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119851</t>
+          <t>118525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>153206</t>
+          <t>151371</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>252256</t>
+          <t>250972</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>295981</t>
+          <t>298562</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>119007</t>
+          <t>118910</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>151865</t>
+          <t>150166</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116978</t>
+          <t>115468</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>151171</t>
+          <t>149859</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>243717</t>
+          <t>244669</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>290133</t>
+          <t>290117</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171374</t>
+          <t>173286</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>207118</t>
+          <t>206955</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>187199</t>
+          <t>190617</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>224661</t>
+          <t>225696</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>370415</t>
+          <t>370427</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>421365</t>
+          <t>421013</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,94%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31255</t>
+          <t>30035</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49793</t>
+          <t>48519</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34173</t>
+          <t>36095</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54140</t>
+          <t>54099</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>70953</t>
+          <t>71419</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>97730</t>
+          <t>96745</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38276</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57989</t>
+          <t>56836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34954</t>
+          <t>34056</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53634</t>
+          <t>53447</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78535</t>
+          <t>77110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105126</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71421</t>
+          <t>72301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92983</t>
+          <t>92215</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82975</t>
+          <t>81545</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>105258</t>
+          <t>103817</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>158290</t>
+          <t>160963</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>190076</t>
+          <t>191246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>174185</t>
+          <t>175191</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>213377</t>
+          <t>213686</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>181207</t>
+          <t>180200</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>219387</t>
+          <t>220090</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>366362</t>
+          <t>367262</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>422108</t>
+          <t>422653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180502</t>
+          <t>179875</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>219455</t>
+          <t>218700</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176142</t>
+          <t>180249</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216724</t>
+          <t>218865</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>368828</t>
+          <t>366803</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426157</t>
+          <t>425607</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>275301</t>
+          <t>273762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>315692</t>
+          <t>317065</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>304196</t>
+          <t>303314</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>347574</t>
+          <t>346567</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>590268</t>
+          <t>589484</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>652471</t>
+          <t>650447</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2903-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2903-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33908</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26677</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>41565</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>40,3%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>31,71%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49,4%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>35351</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28516</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>43677</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>27826</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>42221</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>39,83%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>33908</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>27215</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>41313</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>40,3%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59916</t>
+          <t>59675</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79815</t>
+          <t>79215</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,82%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15333</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22087</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18,22%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,58%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>26,25%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16453</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10761</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22653</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10968</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>23876</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>18,54%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25,52%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15333</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10498</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21750</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>18,22%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40433</t>
+          <t>41278</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>34894</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>27223</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42426</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>41,47%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>32,36%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>50,43%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>36951</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29632</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>44648</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>30316</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>45169</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>41,63%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>33,39%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>50,31%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>34894</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>27352</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>41692</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>41,47%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61442</t>
+          <t>62071</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>81669</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,24%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>84135</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>84135</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>84135</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>88755</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>88755</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>88755</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>84135</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>84135</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>84135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>151914</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>136521</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>168622</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>33,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>29,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>36,74%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>126404</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>111851</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>142668</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>111066</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>142796</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>31,59%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>27,95%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>151914</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>136574</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>167728</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>33,1%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>257440</t>
+          <t>257804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>299947</t>
+          <t>303062</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>94724</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122853</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>23,65%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>20,64%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>26,77%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>80163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>68639</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>91751</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>67868</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>93806</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>20,03%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>17,15%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>22,93%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108515</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>94909</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>123162</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>23,65%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>171416</t>
+          <t>169666</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>209296</t>
+          <t>208664</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>198487</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>182265</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>217515</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>43,25%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39,72%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>47,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>290</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>193628</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>177658</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>210060</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>176520</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>208667</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>48,38%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>44,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>52,49%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>198487</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>181783</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>215925</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>43,25%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>367500</t>
+          <t>366949</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>415245</t>
+          <t>414427</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,24%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>458916</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>458916</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>458916</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>605</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>400195</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>400195</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>400195</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>458916</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>458916</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>458916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39474</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30895</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>48019</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>25,95%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>31,57%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>51445</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>42825</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>61611</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>41616</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>60946</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>30,76%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>25,6%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>36,84%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39474</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>31132</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>48082</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>25,95%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>78235</t>
+          <t>77485</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>104112</t>
+          <t>103565</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>40749</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>31174</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>49219</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,5%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>32,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>37134</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>28830</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>46231</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>28749</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>45893</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>22,2%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,24%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>40749</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>32965</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>50596</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>26,79%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65445</t>
+          <t>66129</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90973</t>
+          <t>91280</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>71871</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>62940</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>82999</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>47,25%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>41,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>54,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>78677</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>68525</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>88653</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>68464</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>89086</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>47,04%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>40,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>53,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>71871</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>62489</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>81414</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>47,25%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135976</t>
+          <t>136788</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165675</t>
+          <t>163854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>152094</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>152094</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>152094</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>167256</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>167256</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>167256</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>152094</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>152094</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>152094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>225295</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>204570</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>243755</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>32,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>35,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>321</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>213200</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>192578</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>231965</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>193917</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>234849</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>32,49%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,35%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>35,35%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>225295</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>206357</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>245801</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>32,41%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>412306</t>
+          <t>411776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>466016</t>
+          <t>468888</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>164597</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>147292</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>182724</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23,68%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>26,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>133750</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>118225</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>150886</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>117719</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>151000</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>20,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>22,99%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>164597</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>145975</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>183928</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>23,68%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274336</t>
+          <t>274482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>323500</t>
+          <t>321514</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>305253</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>284171</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>326296</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>43,91%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>40,88%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>46,94%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>459</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>309256</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>288312</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>328554</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>289545</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>331134</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>47,13%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>43,94%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>50,07%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>305253</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>283820</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>326446</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>585764</t>
+          <t>586845</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>642820</t>
+          <t>643185</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>695144</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>695144</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>695144</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>982</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>656206</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>656206</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>656206</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1046</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>695144</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>695144</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>695144</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2609,7 +2609,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2777,72 +2777,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29298</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22724</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36901</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>35,31%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>27,39%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>44,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>36737</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>29175</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>45190</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>29393</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>44091</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>40,37%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>29298</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>22847</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>38218</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>35,31%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55876</t>
+          <t>55453</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76576</t>
+          <t>76063</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -2890,72 +2890,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14083</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8956</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20289</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16734</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11384</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24527</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10990</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22937</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>18,39%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>26,95%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14083</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9171</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20353</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>16,97%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23392</t>
+          <t>23838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39719</t>
+          <t>39268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -3008,67 +3008,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>39589</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>32477</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>47396</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>47,72%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>39,14%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>57,12%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>37530</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>30332</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>45293</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>30354</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>45410</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>41,24%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>33,33%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>49,77%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>39589</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>30603</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>46849</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>47,72%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66707</t>
+          <t>66655</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88454</t>
+          <t>88413</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,82%</t>
         </is>
       </c>
     </row>
@@ -3116,57 +3116,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>82970</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>82970</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>82970</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>91001</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>91001</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>91001</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>82970</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>82970</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>82970</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3233,72 +3233,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>186793</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>168482</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>204031</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>38,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>34,87%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>42,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>173125</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>155106</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>189745</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>155179</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>191479</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>38,94%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>34,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>42,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>186793</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>171165</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>205715</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>38,66%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>334576</t>
+          <t>332242</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>384982</t>
+          <t>382383</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -3346,72 +3346,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>97438</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>83651</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112531</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>20,16%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>17,31%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>23,29%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>74118</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>62823</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>87931</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>61666</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>87268</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>16,67%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>14,13%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>19,78%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>97438</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>84568</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112148</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>20,16%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>153211</t>
+          <t>153098</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>193325</t>
+          <t>191925</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -3459,72 +3459,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>198981</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>179667</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>215823</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>37,18%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>44,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>284</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>197349</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>180301</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>215195</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>180323</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>215494</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>44,39%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>40,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>48,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>198981</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>180112</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>217125</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>41,18%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>371223</t>
+          <t>374886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>419403</t>
+          <t>423264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,62%</t>
         </is>
       </c>
     </row>
@@ -3572,57 +3572,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>483212</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>483212</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>483212</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>644</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>444591</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>444591</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>444591</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>483212</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>483212</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>483212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3689,72 +3689,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>61443</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>51543</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>72277</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>36,61%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>30,71%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>43,07%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>49846</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41093</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>60745</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>40529</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>59642</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>30,77%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>25,36%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>37,49%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>61443</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>50131</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>71382</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>36,61%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96666</t>
+          <t>97150</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124812</t>
+          <t>126469</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -3802,74 +3802,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>43895</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35460</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>54642</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,16%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21,13%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>32,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>30372</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22846</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>39242</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>22609</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>39236</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>18,75%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,1%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>13,95%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>24,22%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>43895</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>34802</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>54214</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>26,16%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>20,74%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>32,31%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>106</t>
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61408</t>
+          <t>60977</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86836</t>
+          <t>86892</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -3915,72 +3915,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>62479</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>52938</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>73742</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>37,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>31,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>43,94%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>81795</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>70514</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>92141</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>70560</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>91855</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>50,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>56,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>62479</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>52917</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>73960</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>37,23%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128959</t>
+          <t>129215</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>158939</t>
+          <t>158867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,17%</t>
         </is>
       </c>
     </row>
@@ -4028,57 +4028,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167817</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>167817</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>167817</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>162014</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>162014</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>162014</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>167817</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>167817</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>167817</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4145,72 +4145,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>277534</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>254285</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>298027</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>37,81%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,64%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>378</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>259708</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>239779</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>280987</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>240508</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>281654</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>37,23%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34,37%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>40,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>277534</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>256753</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>300163</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>37,81%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>509591</t>
+          <t>509208</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>570095</t>
+          <t>568449</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -4258,72 +4258,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>155417</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>138250</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>173446</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>21,17%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>18,84%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>23,63%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>121224</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>105783</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>138761</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>105901</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>141081</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>17,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>15,16%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>19,89%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>155417</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>137588</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>175244</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>21,17%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>252263</t>
+          <t>253191</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>302481</t>
+          <t>303194</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -4371,72 +4371,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>301049</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>280046</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>323283</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>41,01%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>38,15%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>44,04%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>453</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>316674</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>294882</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>338753</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>291129</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>336944</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>45,39%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>42,27%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>48,56%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>301049</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>278380</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>322306</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>41,01%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>584073</t>
+          <t>585914</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>650109</t>
+          <t>648726</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -4484,57 +4484,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1048</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>734000</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>734000</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>734000</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1005</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>697606</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>697606</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>697606</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1048</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>734000</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>734000</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>734000</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4653,7 +4653,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4664,7 +4664,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4832,72 +4832,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20762</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14985</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27818</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>41,46%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>17049</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11864</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23086</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12374</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>23351</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>29,34%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20762</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>15151</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>27527</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>30,95%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28918</t>
+          <t>29994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46610</t>
+          <t>47095</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -4945,72 +4945,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21667</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15719</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28559</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32,29%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>23,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>17740</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12788</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23876</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12867</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>23928</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>30,53%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>22,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>41,09%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21667</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15638</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28727</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>32,29%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31390</t>
+          <t>32110</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48012</t>
+          <t>48427</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24664</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18091</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>31161</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>36,76%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>26,96%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>46,44%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>23313</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17601</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29304</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17291</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>29575</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>40,12%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>30,29%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>50,43%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24664</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>18328</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>31983</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>36,76%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40038</t>
+          <t>38885</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58208</t>
+          <t>57235</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>45,72%</t>
         </is>
       </c>
     </row>
@@ -5171,57 +5171,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>67093</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>67093</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>67093</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>58102</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>58102</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>58102</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>67093</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>67093</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>67093</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5288,72 +5288,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>135703</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>120318</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>152687</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>28,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>25,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>32,12%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>137577</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>122669</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>154811</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>121624</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>154044</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>29,81%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>26,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>33,55%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>135703</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>118525</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>151371</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>28,55%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>250972</t>
+          <t>250009</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>298562</t>
+          <t>297043</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -5401,72 +5401,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>133008</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>116231</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>149242</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>27,98%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>24,45%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>31,4%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>133957</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>118910</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>150166</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>117654</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>149622</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>29,03%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>25,77%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>32,54%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>133008</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>115468</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>149859</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>27,98%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>244669</t>
+          <t>243018</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>290117</t>
+          <t>289461</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -5514,72 +5514,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>206597</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>188524</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>226688</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>43,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39,66%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>47,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>189925</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>173286</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>206955</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>173838</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>207182</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>41,16%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>44,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>206597</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>190617</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>225696</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>43,47%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>370427</t>
+          <t>373640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>421013</t>
+          <t>422388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -5627,57 +5627,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>475308</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>475308</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>475308</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>697</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>461460</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>461460</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>461460</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>475308</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>475308</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>475308</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5744,72 +5744,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>44086</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35382</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>54523</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>24,36%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>19,55%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>30,12%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>38951</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>30035</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>48519</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>30722</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>48855</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>23,12%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>17,82%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>28,79%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>44086</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>36095</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>54099</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>24,36%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>71419</t>
+          <t>70776</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>96745</t>
+          <t>95971</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -5857,72 +5857,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>43534</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34254</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>53610</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,05%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18,93%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>47361</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>38416</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>56836</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>38395</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>57847</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>28,11%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22,8%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>33,73%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>43534</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>34056</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>53447</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>24,05%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77110</t>
+          <t>78491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>104821</t>
+          <t>104099</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -5970,72 +5970,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>93373</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>82828</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>104364</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>51,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>45,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>57,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>82187</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>72301</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>92215</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>70627</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>91682</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>48,78%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>42,91%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>54,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>93373</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>81545</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>103817</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>51,59%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>160963</t>
+          <t>160306</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>191246</t>
+          <t>190759</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -6083,57 +6083,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>180993</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>180993</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>180993</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>168499</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>168499</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>168499</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>180993</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>180993</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>180993</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6200,72 +6200,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>200551</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>183860</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>222075</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>27,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25,42%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>30,7%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>291</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>193578</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>175191</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>213686</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>174876</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>214060</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>28,13%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>200551</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>180200</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>220090</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>27,72%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>367262</t>
+          <t>367324</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>422653</t>
+          <t>422925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -6313,72 +6313,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>198209</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>179218</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>216562</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>27,4%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29,94%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>199058</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>179875</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>218700</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>180567</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>219236</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>28,93%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>31,79%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>198209</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>180249</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>218865</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>27,4%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366803</t>
+          <t>369875</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425607</t>
+          <t>421711</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -6426,72 +6426,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>324634</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>304775</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>346943</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>44,88%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>42,13%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>47,96%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>295425</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>273762</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>317065</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>272825</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>317407</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>42,94%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>39,79%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>46,08%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>324634</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>303314</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>346567</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>44,88%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>589484</t>
+          <t>589142</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>650447</t>
+          <t>650971</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -6539,57 +6539,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>723394</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>723394</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>723394</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1036</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>688060</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>688060</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>688060</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1034</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>723394</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>723394</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>723394</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
